--- a/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
@@ -596,13 +596,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Import the math module and use math.sqrt to print the square root of a number, rounded to 4 decimal places.
+          <t>Anil's family has bought a square plot for a kitchen garden, and the land record only mentions its total area. To order fencing, Anil needs the length of one side, which is the square root of the area. Import the math module and use math.sqrt to print the square root of the number read from input, rounded to 4 decimal places.
 ### Input Format
 - Line 1: A number
 ### Output Format
 ```
 4.0
 ```
+### Example Walkthrough
+For the sample input, the number is 16. math.sqrt(16) gives 4.0, and rounding to 4 decimal places leaves it as 4.0, so the program prints 4.0.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -741,13 +743,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Use statistics.mean to print the average of a line of numbers, rounded to 2 decimal places.
+          <t>Lakshmi notes down her marks from every weekly quiz and wants to know her average so far, without adding them up by hand. Python's statistics module can do this in one step. Use statistics.mean to print the average of a line of space-separated numbers, rounded to 2 decimal places.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
 ```
 2.5
 ```
+### Example Walkthrough
+For the sample input, the numbers are 1 2 3 4. Their total is 10 and there are 4 numbers, so the mean is 10 / 4 = 2.5, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -886,7 +890,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Use 'from math import gcd' to print the greatest common divisor of two numbers.
+          <t>For Diwali, Deepa has 12 laddus and 18 barfis and wants to pack identical gift boxes with no sweets left over. The largest number of such boxes is the greatest common divisor of the two counts. Use 'from math import gcd' to print the greatest common divisor of the two numbers read from input.
 ### Input Format
 - Line 1: First number
 - Line 2: Second number
@@ -894,6 +898,8 @@
 ```
 6
 ```
+### Example Walkthrough
+For the sample input, the numbers are 12 and 18. The largest number that divides both exactly is 6 (12 = 6 x 2 and 18 = 6 x 3), so gcd(12, 18) returns 6 and the program prints 6.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1040,13 +1046,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Use math.pi to print the area of a circle (pi * r * r) rounded to 2 decimal places.
+          <t>The gardening club is planning a circular flower bed in the middle of the college lawn and needs its area to order the right amount of soil. Instead of typing an approximate value of pi, use the accurate one from the math module. Use math.pi to print the area of a circle (pi * r * r) rounded to 2 decimal places, where r is the radius read from input.
 ### Input Format
 - Line 1: Radius
 ### Output Format
 ```
 3.14
 ```
+### Example Walkthrough
+For the sample input, the radius is 1. The area is math.pi x 1 x 1, which is about 3.14159, and rounding to 2 decimal places gives 3.14, so the program prints 3.14.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1185,13 +1193,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Use collections.Counter to find the most common word in a sentence. Print the word and its count separated by a space.
+          <t>After the college fest, the organisers collect one-line feedback from visitors and want to know which word appears most often across a sentence. Python's collections module has a Counter that makes counting easy. Use collections.Counter to find the most common word in the sentence read from input, and print the word and its count separated by a space.
 ### Input Format
 - Line 1: A sentence
 ### Output Format
 ```
 a 3
 ```
+### Example Walkthrough
+For the sample input, the sentence is 'a b a c a'. Counting each word, 'a' appears 3 times while 'b' and 'c' appear once each, so the most common word is 'a' with count 3 and the program prints 'a 3'.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1331,13 +1341,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Use the datetime module to print the day of the week for a given date (for example 'Monday'). Read a date written as YYYY-MM-DD.
+          <t>Sanya's cousin has fixed a date for the family function, and Sanya wants to check which day of the week it falls on before booking her bus ticket home. Use the datetime module to print the day of the week (for example 'Monday') for a given date. Read a date written as YYYY-MM-DD from input.
 ### Input Format
 - Line 1: A date as YYYY-MM-DD
 ### Output Format
 ```
 Monday
 ```
+### Example Walkthrough
+For the sample input, the date is 2024-01-01, which is 1 January 2024. The datetime module reports that this date falls on a Monday, so the program prints Monday.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1477,13 +1489,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Use the string module's ascii_letters and digits to count how many letters and how many digits are in a line of text. Print the two counts separated by a space.
+          <t>While signing up on a shopping website, users type a line of text, and the site wants to know how much of it is letters and how much is digits. Use the string module's ascii_letters and digits to count how many letters and how many digits are in a line of text read from input. Print the two counts separated by a space.
 ### Input Format
 - Line 1: A line of text
 ### Output Format
 ```
 3 3
 ```
+### Example Walkthrough
+For the sample input, the text is 'abc 123'. The characters a, b, c are letters (3 of them) and 1, 2, 3 are digits (3 of them), while the space is neither, so the program prints '3 3'.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1624,7 +1638,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Use math.comb to print how many ways there are to choose r items from n items.
+          <t>The sports teacher has a squad of players and must pick a few of them for the doubles table-tennis team, and she is curious how many different teams are possible. Choosing r items from n items is exactly what math.comb computes. Use math.comb to print how many ways there are to choose r items from n items, where n and r are read from input.
 ### Input Format
 - Line 1: n
 - Line 2: r
@@ -1632,6 +1646,8 @@
 ```
 10
 ```
+### Example Walkthrough
+For the sample input, n is 5 and r is 2. The number of ways to choose 2 players out of 5 is math.comb(5, 2) = 10, so the program prints 10.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1778,7 +1794,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Use collections.deque and its rotate method to rotate a list of numbers to the right by K places. Print the rotated list separated by spaces.
+          <t>In Varun's hostel, the room-cleaning duty roster shifts every week: each name moves K places to the right, and names that fall off the end come back to the front. Use collections.deque and its rotate method to rotate a list of numbers to the right by K places. Read the numbers and K from input, and print the rotated list separated by spaces.
 ### Input Format
 - Line 1: Space-separated numbers
 - Line 2: K
@@ -1786,6 +1802,8 @@
 ```
 4 5 1 2 3
 ```
+### Example Walkthrough
+For the sample input, the list is 1 2 3 4 5 and K is 2. Rotating right by 2 moves the last two numbers, 4 and 5, to the front, giving 4 5 1 2 3, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1933,7 +1951,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Use fractions.Fraction to add N fractions and print the exact result in lowest terms as 'p/q'. Read N, then N fractions written as 'a/b'.
+          <t>Amma's sweet recipe mixes several part-cup measures of milk, like half a cup and one-third of a cup, and she wants the exact total as a fraction, not a rounded decimal. Use fractions.Fraction to add N fractions and print the exact result in lowest terms as 'p/q'. Read N, then N fractions each written as 'a/b'.
 ### Input Format
 - Line 1: N
 - Next N lines: a fraction 'a/b'
@@ -1941,6 +1959,8 @@
 ```
 5/6
 ```
+### Example Walkthrough
+For the sample input, N is 2 and the fractions are 1/2 and 1/3. Writing both with denominator 6 gives 3/6 + 2/6 = 5/6, which is already in lowest terms, so the program prints '5/6'.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -604,7 +604,7 @@
 4.0
 ```
 ### Example Walkthrough
-For the sample input, the number is 16. math.sqrt(16) gives 4.0, and rounding to 4 decimal places leaves it as 4.0, so the program prints 4.0.
+For the sample input, the number is 16. math.`sqrt(16)` gives 4.0, and rounding to 4 decimal places leaves it as 4.0, so the program prints 4.0.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -899,7 +899,7 @@
 6
 ```
 ### Example Walkthrough
-For the sample input, the numbers are 12 and 18. The largest number that divides both exactly is 6 (12 = 6 x 2 and 18 = 6 x 3), so gcd(12, 18) returns 6 and the program prints 6.
+For the sample input, the numbers are 12 and 18. The largest number that divides both exactly is 6 (12 = 6 x 2 and 18 = 6 x 3), so `gcd(12, 18)` returns 6 and the program prints 6.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>While signing up on a shopping website, users type a line of text, and the site wants to know how much of it is letters and how much is digits. Use the string module's ascii_letters and digits to count how many letters and how many digits are in a line of text read from input. Print the two counts separated by a space.
+          <t>While signing up on a shopping website, users type a line of text, and the site wants to know how much of it is letters and how much is digits. Use the string module's `ascii_letters` and digits to count how many letters and how many digits are in a line of text read from input. Print the two counts separated by a space.
 ### Input Format
 - Line 1: A line of text
 ### Output Format
@@ -1647,7 +1647,7 @@
 10
 ```
 ### Example Walkthrough
-For the sample input, n is 5 and r is 2. The number of ways to choose 2 players out of 5 is math.comb(5, 2) = 10, so the program prints 10.
+For the sample input, n is 5 and r is 2. The number of ways to choose 2 players out of 5 is math.`comb(5, 2)` = 10, so the program prints 10.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,7 +607,7 @@
 4.0
 ```
 ### Example Walkthrough
-For the sample input, the number is 16. math.`sqrt(16)` gives 4.0, and rounding to 4 decimal places leaves it as 4.0, so the program prints 4.0.
+For the sample input, the number is 16. `math.sqrt(16)` gives 4.0, and rounding to 4 decimal places leaves it as 4.0, so the program prints 4.0.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -620,22 +623,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>standard-library</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>standard-library</t>
+          <t>math-module</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -767,22 +780,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>modules-and-packages</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>standard-library</t>
+          <t>importing-modules</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -915,22 +938,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>standard-library</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>math-module</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1070,22 +1103,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>standard-library</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>standard-library</t>
+          <t>math-module</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1217,22 +1260,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>modules-and-packages</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>standard-library</t>
+          <t>importing-modules</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1365,22 +1418,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>standard-library</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>standard-library</t>
+          <t>datetime-module</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1513,22 +1576,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>modules-and-packages</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>standard-library</t>
+          <t>importing-modules</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1647,7 +1720,7 @@
 10
 ```
 ### Example Walkthrough
-For the sample input, n is 5 and r is 2. The number of ways to choose 2 players out of 5 is math.`comb(5, 2)` = 10, so the program prints 10.
+For the sample input, n is 5 and r is 2. The number of ways to choose 2 players out of 5 is `math.comb(5, 2)` = 10, so the program prints 10.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1663,22 +1736,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>standard-library</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>standard-library</t>
+          <t>math-module</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1789,10 +1872,505 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Radians to Degrees</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Radians to Degrees. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Radians
+### Output Format
+```
+180.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>standard-library</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3.141592653589793</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1.5707963267948966</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6.283185307179586</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>114.59</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>import math
+print(round(math.degrees(float(input())),2))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Random Choice Seed</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Random Choice Seed. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Seed
+### Output Format
+```
+blue
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>standard-library</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>random-module</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>import random
+random.seed(int(input()))
+print(random.choice(["red","blue","green","yellow"]))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Rotate with Deque</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>In Varun's hostel, the room-cleaning duty roster shifts every week: each name moves K places to the right, and names that fall off the end come back to the front. Use collections.deque and its rotate method to rotate a list of numbers to the right by K places. Read the numbers and K from input, and print the rotated list separated by spaces.
 ### Input Format
@@ -1809,131 +2387,141 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 2</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>4 5 1 2 3</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1 2 3
 0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>1 2
 3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>2 1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 5</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 -2</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>3 4 5 1 2</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 10</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>7 8 1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>from collections import deque
 nums = deque(map(int, input().split()))
@@ -1943,13 +2531,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Sum of Fractions</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Amma's sweet recipe mixes several part-cup measures of milk, like half a cup and one-third of a cup, and she wants the exact total as a fraction, not a rounded decimal. Use fractions.Fraction to add N fractions and print the exact result in lowest terms as 'p/q'. Read N, then N fractions each written as 'a/b'.
 ### Input Format
@@ -1966,77 +2554,87 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>2
 1/2
 1/3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>5/6</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1
 2/4</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>3
 1/6
@@ -2044,33 +2642,33 @@
 1/6</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1
 0/1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>4
 1/2
@@ -2079,24 +2677,24 @@
 1/2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>2/1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2
 1/3
 2/3</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>from fractions import Fraction
 n = int(input())
@@ -2107,13 +2705,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Factorial from Math</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Use math.factorial to print the factorial of a number read from input.
 ### Input Format
@@ -2122,142 +2720,154 @@
 ```
 120
 ```
+### Example Walkthrough
+In the sample, the number is `5`. Its factorial is `5 x 4 x 3 x 2 x 1 = 120`, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>3628800</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>5040</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>479001600</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>import math
 print(math.factorial(int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Floor and Ceiling</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read a decimal number and use math.floor and math.ceil to print its floor and ceiling, separated by a space.
 ### Input Format
@@ -2266,129 +2876,141 @@
 ```
 3 4
 ```
+### Example Walkthrough
+In the sample, the number is `3.2`. Its floor is `3` and its ceiling is `4`, so the program prints `3 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3 4</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>5 5</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>-2.5</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>-3 -2</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>-1 0</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>99.99</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>99 100</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>-100.01</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>-101 -100</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>import math
 x = float(input())
@@ -2396,13 +3018,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Median with Statistics</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Use statistics.median to print the median of a line of numbers.
 ### Input Format
@@ -2411,129 +3033,141 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3`. The middle value is `2`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-3 -1 -2</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>import statistics
 nums = list(map(int, input().split()))
@@ -2541,13 +3175,13 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Power from Math</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Use math.pow to print a raised to the power b as a whole number.
 ### Input Format
@@ -2557,136 +3191,148 @@
 ```
 1024
 ```
+### Example Walkthrough
+In the sample, the base is `2` and the exponent is `10`. Computing `2` raised to the power `10` gives `1024`, so the program prints `1024`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>3
 0</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>5
 2</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1
 100</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>10
 1</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>-2
 3</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>import math
 base = int(input())
@@ -2695,13 +3341,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Hypotenuse</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Use math.hypot to print the length of the hypotenuse of a right triangle given its two shorter sides, rounded to 2 decimal places.
 ### Input Format
@@ -2711,136 +3357,148 @@
 ```
 5.0
 ```
+### Example Walkthrough
+In the sample, the two sides are `3` and `4`. The hypotenuse is `sqrt(3^2 + 4^2) = 5.0`, so the program prints `5.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>5
 12</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>8
 15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>17.0</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>141.42</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>import math
 a = int(input())
@@ -2849,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Base-10 Logarithm</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Use math.log10 to print the base-10 logarithm of a number, rounded to 4 decimal places.
 ### Input Format
@@ -2864,129 +3522,141 @@
 ```
 2.0
 ```
+### Example Walkthrough
+In the sample, the number is `100`. Its base-10 logarithm is `2.0`, so the program prints `2.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.699</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2.9996</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
@@ -2994,13 +3664,516 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Days Difference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Days Difference. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First date
+- Line 2: Second date
+### Output Format
+```
+1
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>standard-library</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>datetime-module</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-01-01
+2026-01-02</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-01-10
+2026-01-01</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2024-02-28
+2024-03-01</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-07-09
+2026-07-09</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2025-12-31
+2026-01-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2020-01-01
+2020-01-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-05-01
+2026-04-01</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>from datetime import datetime
+a=datetime.strptime(input(),"%Y-%m-%d"); b=datetime.strptime(input(),"%Y-%m-%d")
+print(abs((b-a).days))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Import Alias Sqrt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Import Alias Sqrt. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Number
+### Output Format
+```
+4
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>import math as m
+print(m.isqrt(int(input())))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Standard Deviation</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Use statistics.pstdev to print the population standard deviation of a line of numbers, rounded to 2 decimal places.
 ### Input Format
@@ -3009,129 +4182,141 @@
 ```
 1.41
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5`. Their population standard deviation, rounded to 2 decimal places, is `1.41`, so the program prints `1.41`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>10 10 10</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>-5 5 -5 5</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>2.87</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>100 200</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>import statistics
 nums = list(map(int, input().split()))
@@ -3139,13 +4324,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - GCD of a List</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Use functools.reduce together with math.gcd to print the greatest common divisor of a whole line of numbers.
 ### Input Format
@@ -3154,129 +4339,141 @@
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the numbers are `12 18 24`. Their greatest common divisor is `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>import</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>standard-library</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>12 18 24</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>7 14</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>100 25 50</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0 5</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1000 500 250 100</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>from functools import reduce
 from math import gcd
@@ -3285,13 +4482,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Count Permutations</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Use math.perm to print how many ordered arrangements there are of r items chosen from n items.
 ### Input Format
@@ -3301,136 +4498,148 @@
 ```
 20
 ```
+### Example Walkthrough
+In the sample, `n` is `5` and `r` is `2`. The number of ordered arrangements of `2` items from `5` is `5 x 4 = 20`, so the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>5
 2</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>4
 4</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>6
 1</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>10
 0</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
@@ -3439,13 +4648,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Group by Parity</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Use collections.defaultdict to split a line of numbers into evens and odds. Print 'even:' followed by the even numbers, then 'odd:' followed by the odd numbers, keeping their original order.
 ### Input Format
@@ -3455,136 +4664,148 @@
 even: 2 4
 odd: 1 3 5
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5`. The even ones are `2` and `4`, and the odd ones are `1`, `3`, and `5`, so the program prints `even: 2 4` then `odd: 1 3 5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>even: 2 4
 odd: 1 3 5</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>even: 2 4
 odd:</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1 3</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>even:
 odd: 1 3</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>even: 0
 odd:</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>-2 -1 0 1 2</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>even: -2 0 2
 odd: -1 1</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>even: 2 4 6 8 10
 odd: 1 3 5 7 9</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>even:
 odd: 7</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>from collections import defaultdict
 groups = defaultdict(list)
@@ -3595,13 +4816,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Seeded Random</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Use the random module. Read a seed, seed the generator with it, and print a single random integer from 1 to 100. Seeding makes the result repeatable.
 ### Input Format
@@ -3610,129 +4831,141 @@
 ```
 18
 ```
+### Example Walkthrough
+In the sample, the seed is `1`. Seeding the generator with `1` and then requesting a random integer from `1` to `100` deterministically produces `18`, so the program prints `18`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>random-module</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>12345</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>import random
 seed = int(input())
@@ -3741,13 +4974,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Find the Mode</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Use statistics.mode to print the value that appears most often in a line of numbers.
 ### Input Format
@@ -3756,129 +4989,141 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 2 3`. The value `2` appears most often, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>1 2 2 3</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1 1 2 2</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>-1 -1 -2</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>1 2 3 3 3 4</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>9 9 9 9 9 9</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>import statistics
 nums = list(map(int, input().split()))
@@ -3886,13 +5131,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Top K Words</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Use collections.Counter to print the K most common words in a sentence, one 'word count' per line, from most to least common.
 ### Input Format
@@ -3903,118 +5148,130 @@
 a 3
 b 2
 ```
+### Example Walkthrough
+In the sample, `K` is `2` and the sentence is `a b a c a b`. The word `a` appears `3` times and `b` appears `2` times, more than `c`, so the program prints `a 3` then `b 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>2
 a b a c b a</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>a 3
 b 2</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1
 x x y</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>x 2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>3
 p q r</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>p 1
 q 1
 r 1</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1
 z</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>z 1</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0
 a b c</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>5
 a a b b c c d</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>a 2
 b 2
@@ -4022,19 +5279,19 @@
 d 1</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2
 cat cat dog dog dog bird</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>dog 3
 cat 2</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>from collections import Counter
 k = int(input())
@@ -4044,13 +5301,658 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Path Suffix</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Path Suffix. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Path
+### Output Format
+```
+.csv
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>standard-library</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pathlib-module</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>report.csv</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>.csv</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>/tmp/data.json</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>.json</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>archive.tar.gz</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>.gz</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>notes.txt</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>.txt</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>a/b/c.py</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>.py</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>image.PNG</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>.PNG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>from pathlib import Path
+print(Path(input()).suffix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Counter Import</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Counter Import. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Word
+### Output Format
+```
+a 3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>banana</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>a 3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>l 2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>a 1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>mississippi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>i 4</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>bookkeeper</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>e 3</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>112233</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>zzzy</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>z 3</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>from collections import Counter
+ch,c=Counter(input()).most_common(1)[0]
+print(ch,c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - OS Basename</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for OS Basename. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Path
+### Output Format
+```
+a.txt
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>standard-library</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>os-module</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>/home/user/a.txt</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>a.txt</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>report.csv</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>report.csv</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>folder/sub/file.py</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>file.py</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>/tmp/</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>tmp</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>C:/data/test.txt</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>test.txt</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>a/b/c</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>import os
+print(os.path.basename(input().rstrip("/")))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Pairs from Combinations</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Use itertools.combinations to count how many pairs of numbers add up to a target. Read a line of numbers and a target and print the count.
 ### Input Format
@@ -4060,136 +5962,148 @@
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the numbers are `1 2 3 4 5` and the target is `6`. The pairs `(1, 5)` and `(2, 4)` both add up to `6`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1 2 3 4
 5</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1 1 1
 2</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>5 6
 100</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0 0 0
 0</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 9</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>-1 1 -2 2
 0</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>from itertools import combinations
 nums = list(map(int, input().split()))
@@ -4198,13 +6112,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Days Between Dates</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Use the datetime module to print how many days apart two dates are (a non-negative number). Read two dates written as YYYY-MM-DD.
 ### Input Format
@@ -4214,136 +6128,148 @@
 ```
 30
 ```
+### Example Walkthrough
+In the sample, the dates are `2024-01-01` and `2024-01-31`. They are `30` days apart, so the program prints `30`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>datetime-module</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>2024-01-01
 2024-01-31</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2024-01-01
 2024-01-01</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2020-01-01
 2021-01-01</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>366</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2024-03-01
 2024-01-01</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1970-01-01
 1970-01-01</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2000-02-29
 2000-03-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1999-12-31
 2000-01-01</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>from datetime import date
 def parse(s):
@@ -4355,13 +6281,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Common Words with Counts</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Use Counter intersection (the &amp; operator) to find words appearing in both of two lines. For each shared word in sorted order, print 'word:count' where count is the smaller of the two counts.
 ### Input Format
@@ -4372,128 +6298,140 @@
 a:1
 b:1
 ```
+### Example Walkthrough
+In the sample, the sentences are `a b c` and `a b d`. The words `a` and `b` appear in both, once each, so the program prints `a:1` then `b:1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>a a b c
 a b b</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>a:1
 b:1</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>x y
 y z</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>y:1</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>p p
 p p p</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>p:2</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>x
 x</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>x:1</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>a b c d
 e f g h</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>cat cat dog
 dog dog cat</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>cat:1
 dog:1</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>from collections import Counter
 c1 = Counter(input().split())
@@ -4504,13 +6442,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Leap Year Check</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Use calendar.isleap to print 'Yes' if a year is a leap year and 'No' otherwise.
 ### Input Format
@@ -4519,129 +6457,141 @@
 ```
 Yes
 ```
+### Example Walkthrough
+In the sample, the year is `2024`, which is divisible by `4` and not a century year, so it is a leap year and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>import calendar
 year = int(input())
@@ -4649,13 +6599,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Exact Decimal Sum</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Use decimal.Decimal to add two decimal numbers without floating-point rounding error, and print the exact sum. Read the two numbers as text.
 ### Input Format
@@ -4665,136 +6615,148 @@
 ```
 0.3
 ```
+### Example Walkthrough
+In the sample, the numbers are `0.1` and `0.2`. Using `Decimal` avoids floating-point rounding error, so the exact sum `0.3` is printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.1
 0.2</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1.5
 2.5</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0.01
 0.02</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-1.5
 1.5</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>100.001
 0.999</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>101.000</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>-0.1
 -0.2</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>from decimal import Decimal
 a = Decimal(input())
@@ -4803,13 +6765,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - K Largest with Heapq</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Use heapq.nlargest to print the K largest numbers from a list, in descending order, separated by spaces.
 ### Input Format
@@ -4819,131 +6781,143 @@
 ```
 5 4
 ```
+### Example Walkthrough
+In the sample, `K` is `2` and the numbers are `3 1 4 1 5`. The two largest values are `5` and `4`, so the program prints `5 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>standard-library</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>2
 3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>5 4</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1
 7 2</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3
 5 5 5</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 1 2 3</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>5
 1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>10 9 8 7 6</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2
 -5 -1 -10</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>-1 -5</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>import heapq
 k = int(input())
@@ -4952,13 +6926,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Prime Factors</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Use math.isqrt to help print the prime factors of a number in increasing order, separated by spaces (a factor is listed once for each time it divides the number).
 ### Input Format
@@ -4967,129 +6941,141 @@
 ```
 2 2 3
 ```
+### Example Walkthrough
+In the sample, the number is `12`. Its prime factors are `2`, `2`, and `3` (since `2 x 2 x 3 = 12`), so the program prints `2 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>modules</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>math-module</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>2 2 3</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>2 2 3 5</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2 2 2 2 2 2 2 2 2 2</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>3 3 3 37</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
@@ -5106,6 +7092,484 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Decimal Addition</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Decimal Addition. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First
+- Line 2: Second
+### Output Format
+```
+0.3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.1
+0.2</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.5
+2.25</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>100
+0.01</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>100.01</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-1.1
+1.1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>999.99
+0.01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0
+0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>123.456
+0.004</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>123.460</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>from decimal import Decimal
+print(Decimal(input())+Decimal(input()))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Permutations Count</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Permutations Count. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Items
+- Line 2: R
+### Output Format
+```
+6
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>modules-and-packages</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>importing-modules</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>a b c
+2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>x y
+2</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1 2 3 4
+1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>a
+1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>p q r
+3</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>a b c d
+2</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>z
+0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>from itertools import permutations
+print(sum(1 for _ in permutations(input().split(), int(input()))))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Date Month Name</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Date Month Name. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Date
+### Output Format
+```
+July
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>standard-library</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>datetime-module</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1999-09-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2030-03-01</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>from datetime import datetime
+print(datetime.strptime(input(),"%Y-%m-%d").strftime("%B"))</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
@@ -1877,16 +1877,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Radians to Degrees. Read the input values and print the required result exactly.
+          <t>A robotics engineer's sensor reports the rotation angle of a robotic arm joint in radians, but the control panel needs to display the angle in degrees. Import the math module and use math.degrees to convert the radian value read from input into degrees, rounding the result to 2 decimal places before printing.
 ### Input Format
-- Line 1: Radians
+- Line 1: Angle in radians
 ### Output Format
 ```
 180.0
 ```
+### Example Walkthrough
+For the sample input, the angle is 3.141592653589793 radians (which is pi). `math.degrees(3.141592653589793)` gives 180.0 exactly, and rounding to 2 decimal places leaves it as 180.0, so the program prints 180.0.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2031,16 +2033,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Random Choice Seed. Read the input values and print the required result exactly.
+          <t>A game developer is testing a color-picker wheel for a mobile app and needs the "random" pick to be reproducible for automated tests, so the wheel's random number generator is seeded with a fixed value before picking. Import the random module, seed it with the integer read from input using random.seed, and then use random.choice to print one color chosen from the fixed list ["red", "blue", "green", "yellow"] (in that exact order).
 ### Input Format
-- Line 1: Seed
+- Line 1: Seed value (integer)
 ### Output Format
 ```
 blue
 ```
+### Example Walkthrough
+For the sample input, the seed is 1. Seeding Python's random generator with `random.seed(1)` and then calling `random.choice(["red","blue","green","yellow"])` deterministically returns "blue" for this seed, so the program prints blue.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The seed is always a valid integer.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3672,17 +3676,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Days Difference. Read the input values and print the required result exactly.
+          <t>A project manager tracks milestone dates in YYYY-MM-DD format and needs to quickly calculate the number of days between any two milestones. Import datetime from the datetime module, parse both input dates with datetime.strptime using the format "%Y-%m-%d", subtract them to get a timedelta, and print the absolute value of the number of days between the two dates.
 ### Input Format
-- Line 1: First date
-- Line 2: Second date
+- Line 1: First date (YYYY-MM-DD)
+- Line 2: Second date (YYYY-MM-DD)
 ### Output Format
 ```
 1
 ```
+### Example Walkthrough
+For the sample input, the dates are 2026-01-01 and 2026-01-02. Parsing both with `datetime.strptime` and subtracting gives a difference of 1 day, and taking the absolute value keeps it 1, so the program prints 1.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Both dates are valid calendar dates in YYYY-MM-DD format.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3835,16 +3841,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Import Alias Sqrt. Read the input values and print the required result exactly.
+          <t>A tiler is arranging square tiles to cover the largest possible square area within a plot of a given number of unit tiles, and needs the largest whole number whose square does not exceed that count. Import the math module using the alias "m" (import math as m), and use m.isqrt to print the integer square root of the number read from input — the floor of the exact square root.
 ### Input Format
-- Line 1: Number
+- Line 1: A whole number
 ### Output Format
 ```
 4
 ```
+### Example Walkthrough
+For the sample input, the number is 16. `m.isqrt(16)` returns 4, since 4 x 4 = 16 exactly, so the program prints 4.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a non-negative integer.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5309,16 +5317,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Path Suffix. Read the input values and print the required result exactly.
+          <t>A file-organizing script needs to sort documents into folders based on their file type, which it can determine from the file extension (suffix) of the file name. Import Path from the pathlib module and use the .suffix attribute to print the file extension (including the leading dot) of the file path read from input; if the file name has no extension, .suffix is an empty string.
 ### Input Format
-- Line 1: Path
+- Line 1: A file path or file name
 ### Output Format
 ```
 .csv
 ```
+### Example Walkthrough
+For the sample input, the path is "report.csv". `Path("report.csv").suffix` returns ".csv", the last extension of the file name, so the program prints .csv.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid file path or file name string.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5413,7 +5423,6 @@
           <t>README</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr">
         <is>
           <t>notes.txt</t>
@@ -5459,16 +5468,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Counter Import. Read the input values and print the required result exactly.
+          <t>A text-analysis tool needs to find the most frequently occurring character in a word, for example to detect repeated letters in log tags. Import Counter from the collections module, build a Counter of the characters in the input string, and use .most_common(1) to get the single most frequent character and its count; print the character and count separated by a space.
 ### Input Format
-- Line 1: Word
+- Line 1: A word (string)
 ### Output Format
 ```
 a 3
 ```
+### Example Walkthrough
+For the sample input, the word is "banana". Counting characters gives a:3, b:1, n:2, so the most common character is "a" with a count of 3, and the program prints a 3.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a non-empty string of characters.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5614,16 +5625,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for OS Basename. Read the input values and print the required result exactly.
+          <t>A log-processing script receives full file paths from different servers and needs to extract just the file name for display, ignoring the directory structure. Import the os module and use os.path.basename to print the final component (file or folder name) of the path read from input, after stripping any trailing slash.
 ### Input Format
-- Line 1: Path
+- Line 1: A file or directory path
 ### Output Format
 ```
 a.txt
 ```
+### Example Walkthrough
+For the sample input, the path is "/home/user/a.txt". `os.path.basename` returns the last component after the final slash, which is "a.txt", so the program prints a.txt.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid file or directory path string.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7100,17 +7113,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Decimal Addition. Read the input values and print the required result exactly.
+          <t>An accountant adding up small currency amounts finds that ordinary floating-point addition in Python sometimes produces tiny rounding errors (like 0.1 + 0.2 giving 0.30000000000000004), so the billing script uses exact decimal arithmetic instead. Import Decimal from the decimal module, convert both input values to Decimal, add them, and print the exact sum.
 ### Input Format
-- Line 1: First
-- Line 2: Second
+- Line 1: First number
+- Line 2: Second number
 ### Output Format
 ```
 0.3
 ```
+### Example Walkthrough
+For the sample input, the numbers are 0.1 and 0.2. Adding them as `Decimal("0.1") + Decimal("0.2")` gives exactly 0.3 (unlike ordinary float addition), so the program prints 0.3.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Both inputs are valid decimal numbers.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7262,17 +7277,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Permutations Count. Read the input values and print the required result exactly.
+          <t>An event organizer wants to know how many different ways a subset of contestants can be arranged on stage for the first few award positions, given a list of contestant names and the number of positions to fill. Import permutations from the itertools module, split the first input line into a list of items, and use itertools.permutations to print the count of all possible ordered arrangements of the given size R (the second input line).
 ### Input Format
-- Line 1: Items
-- Line 2: R
+- Line 1: Space-separated items
+- Line 2: R (the arrangement size)
 ### Output Format
 ```
 6
 ```
+### Example Walkthrough
+For the sample input, the items are "a b c" (3 items) and R is 2. The number of ordered arrangements of 2 items chosen from 3 is `permutations(["a","b","c"], 2)`, which yields 6 arrangements (ab, ac, ba, bc, ca, cb), so the program prints 6.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- R is a non-negative integer not greater than the number of items.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7424,16 +7441,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Date Month Name. Read the input values and print the required result exactly.
+          <t>A calendar app displays event dates to users with the full month name instead of a numeric month, to make the schedule easier to read. Import datetime from the datetime module, parse the input date using datetime.strptime with the format "%Y-%m-%d", and use strftime("%B") to print the full English month name of that date.
 ### Input Format
-- Line 1: Date
+- Line 1: A date in YYYY-MM-DD format
 ### Output Format
 ```
 July
 ```
+### Example Walkthrough
+For the sample input, the date is "2026-07-09". Parsing it with `datetime.strptime` gives month 07, and `strftime("%B")` converts month 07 to its full name, "July", so the program prints July.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid calendar date in YYYY-MM-DD format.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
@@ -1877,15 +1877,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A robotics engineer's sensor reports the rotation angle of a robotic arm joint in radians, but the control panel needs to display the angle in degrees. Import the math module and use math.degrees to convert the radian value read from input into degrees, rounding the result to 2 decimal places before printing.
+          <t>A robotics workshop programs a servo arm using angles in radians internally, but the control panel needs to display the equivalent angle in degrees for the technician operating it.
+Import the `math` module and use `math.degrees` to convert an angle from radians to degrees, then print the result rounded to 2 decimal places.
 ### Input Format
-- Line 1: Angle in radians
+- Line 1: An angle in radians
 ### Output Format
 ```
 180.0
 ```
 ### Example Walkthrough
-For the sample input, the angle is 3.141592653589793 radians (which is pi). `math.degrees(3.141592653589793)` gives 180.0 exactly, and rounding to 2 decimal places leaves it as 180.0, so the program prints 180.0.
+In the sample, the angle is `3.141592653589793` radians (pi). `math.degrees(pi)` gives 180.0, so the program prints `180.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2033,17 +2034,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A game developer is testing a color-picker wheel for a mobile app and needs the "random" pick to be reproducible for automated tests, so the wheel's random number generator is seeded with a fixed value before picking. Import the random module, seed it with the integer read from input using random.seed, and then use random.choice to print one color chosen from the fixed list ["red", "blue", "green", "yellow"] (in that exact order).
+          <t>A raffle app picks a winning color from four options, but for demo purposes the organizers want the pick to be reproducible: seeding the random number generator with a fixed number before choosing means the same seed always produces the same result.
+Import the `random` module, call `random.seed` with a whole number read from input, then use `random.choice` to pick one value from the list `["red", "blue", "green", "yellow"]` and print it.
 ### Input Format
-- Line 1: Seed value (integer)
+- Line 1: A whole number used as the random seed
 ### Output Format
 ```
 blue
 ```
 ### Example Walkthrough
-For the sample input, the seed is 1. Seeding Python's random generator with `random.seed(1)` and then calling `random.choice(["red","blue","green","yellow"])` deterministically returns "blue" for this seed, so the program prints blue.
+In the sample, the seed is 1. Seeding Python's random module with 1 and then calling `random.choice` on the color list deterministically picks `blue`, so the program prints `blue`.
 ### Constraints
-- The seed is always a valid integer.
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -3676,7 +3678,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A project manager tracks milestone dates in YYYY-MM-DD format and needs to quickly calculate the number of days between any two milestones. Import datetime from the datetime module, parse both input dates with datetime.strptime using the format "%Y-%m-%d", subtract them to get a timedelta, and print the absolute value of the number of days between the two dates.
+          <t>A hotel booking app calculates the number of nights between a guest's check-in date and check-out date, regardless of which one was typed first.
+Import `datetime` from the `datetime` module, read two dates in `YYYY-MM-DD` format, and print the absolute number of days between them.
 ### Input Format
 - Line 1: First date (YYYY-MM-DD)
 - Line 2: Second date (YYYY-MM-DD)
@@ -3685,9 +3688,9 @@
 1
 ```
 ### Example Walkthrough
-For the sample input, the dates are 2026-01-01 and 2026-01-02. Parsing both with `datetime.strptime` and subtracting gives a difference of 1 day, and taking the absolute value keeps it 1, so the program prints 1.
+In the sample, the dates are `2026-01-01` and `2026-01-02`. The difference between them is 1 day, so the program prints `1`.
 ### Constraints
-- Both dates are valid calendar dates in YYYY-MM-DD format.
+- Dates are valid and formatted as `YYYY-MM-DD`.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -3841,7 +3844,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A tiler is arranging square tiles to cover the largest possible square area within a plot of a given number of unit tiles, and needs the largest whole number whose square does not exceed that count. Import the math module using the alias "m" (import math as m), and use m.isqrt to print the integer square root of the number read from input — the floor of the exact square root.
+          <t>A packing app calculates the largest complete square grid of boxes that fit inside a warehouse holding N boxes total, using an integer square root so the result is always a whole number of boxes per side.
+Import the `math` module under the shorter alias `m` (`import math as m`), then use `m.isqrt` to compute the integer square root of a whole number read from input, and print the result.
 ### Input Format
 - Line 1: A whole number
 ### Output Format
@@ -3849,9 +3853,9 @@
 4
 ```
 ### Example Walkthrough
-For the sample input, the number is 16. `m.isqrt(16)` returns 4, since 4 x 4 = 16 exactly, so the program prints 4.
+In the sample, the number is 16. `m.isqrt(16)` returns 4 (since 4 x 4 = 16 exactly), so the program prints `4`.
 ### Constraints
-- The input is a non-negative integer.
+- All numeric inputs are valid non-negative whole numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5317,17 +5321,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A file-organizing script needs to sort documents into folders based on their file type, which it can determine from the file extension (suffix) of the file name. Import Path from the pathlib module and use the .suffix attribute to print the file extension (including the leading dot) of the file path read from input; if the file name has no extension, .suffix is an empty string.
+          <t>A file upload service checks the extension of every uploaded file's name to decide which validator to run, using the `Path` class from the `pathlib` module instead of manually searching for the last dot.
+Import `Path` from the `pathlib` module, read a file name or path, and print its file extension (including the leading dot) using the `.suffix` property. If the file has no extension, print an empty line.
 ### Input Format
-- Line 1: A file path or file name
+- Line 1: A file name or path
 ### Output Format
 ```
 .csv
 ```
 ### Example Walkthrough
-For the sample input, the path is "report.csv". `Path("report.csv").suffix` returns ".csv", the last extension of the file name, so the program prints .csv.
+In the sample, the input is `report.csv`. `Path("report.csv").suffix` returns `.csv`, so the program prints `.csv`.
 ### Constraints
-- The input is a valid file path or file name string.
+- The input is a valid file name or path.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5468,17 +5473,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A text-analysis tool needs to find the most frequently occurring character in a word, for example to detect repeated letters in log tags. Import Counter from the collections module, build a Counter of the characters in the input string, and use .most_common(1) to get the single most frequent character and its count; print the character and count separated by a space.
+          <t>A word-frequency analyzer needs to know which single character appears most often in a block of text, using the `Counter` class from the `collections` module to tally every character instantly instead of writing a manual loop.
+Import `Counter` from the `collections` module, read a line of text, and use `Counter` together with `most_common(1)` to find the character that appears most often and how many times it appears, then print the character and the count separated by a space.
 ### Input Format
-- Line 1: A word (string)
+- Line 1: A line of text
 ### Output Format
 ```
 a 3
 ```
 ### Example Walkthrough
-For the sample input, the word is "banana". Counting characters gives a:3, b:1, n:2, so the most common character is "a" with a count of 3, and the program prints a 3.
+In the sample, the text is `banana`. Counting each character, `a` appears 3 times, more than any other character, so the program prints `a 3`.
 ### Constraints
-- The input is a non-empty string of characters.
+- The input is a valid, non-empty line of text.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -5625,17 +5631,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A log-processing script receives full file paths from different servers and needs to extract just the file name for display, ignoring the directory structure. Import the os module and use os.path.basename to print the final component (file or folder name) of the path read from input, after stripping any trailing slash.
+          <t>A file manager app needs to display just the file (or folder) name at the end of a full file path, without the rest of the directory structure, using the `os.path` module instead of splitting the string manually.
+Import the `os` module, read a file path, and print just the final component of the path (the file or folder name) using `os.path.basename`, after removing any trailing slash.
 ### Input Format
-- Line 1: A file or directory path
+- Line 1: A file path
 ### Output Format
 ```
 a.txt
 ```
 ### Example Walkthrough
-For the sample input, the path is "/home/user/a.txt". `os.path.basename` returns the last component after the final slash, which is "a.txt", so the program prints a.txt.
+In the sample, the path is `/home/user/a.txt`. `os.path.basename` returns just the final component, `a.txt`, which the program prints.
 ### Constraints
-- The input is a valid file or directory path string.
+- The input is a valid file path.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7113,18 +7120,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>An accountant adding up small currency amounts finds that ordinary floating-point addition in Python sometimes produces tiny rounding errors (like 0.1 + 0.2 giving 0.30000000000000004), so the billing script uses exact decimal arithmetic instead. Import Decimal from the decimal module, convert both input values to Decimal, add them, and print the exact sum.
+          <t>A billing system adds two currency amounts together and must avoid the tiny rounding errors that plain floating-point addition can introduce (like `0.1 + 0.2` not printing exactly `0.3`), so it uses the `Decimal` class from the `decimal` module instead.
+Import `Decimal` from the `decimal` module, read two numbers as text, convert each to a `Decimal`, and print their sum.
 ### Input Format
-- Line 1: First number
-- Line 2: Second number
+- Line 1: First amount
+- Line 2: Second amount
 ### Output Format
 ```
 0.3
 ```
 ### Example Walkthrough
-For the sample input, the numbers are 0.1 and 0.2. Adding them as `Decimal("0.1") + Decimal("0.2")` gives exactly 0.3 (unlike ordinary float addition), so the program prints 0.3.
+In the sample, the amounts are `0.1` and `0.2`. Adding them as `Decimal` values gives exactly `0.3`, with none of the rounding drift that ordinary floating-point addition can produce, so the program prints `0.3`.
 ### Constraints
-- Both inputs are valid decimal numbers.
+- The inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7277,18 +7285,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>An event organizer wants to know how many different ways a subset of contestants can be arranged on stage for the first few award positions, given a list of contestant names and the number of positions to fill. Import permutations from the itertools module, split the first input line into a list of items, and use itertools.permutations to print the count of all possible ordered arrangements of the given size R (the second input line).
+          <t>An event scheduler needs to know how many different ways it can arrange a subset of R speakers, in order, from a longer list of available speakers, using `itertools.permutations` to count the arrangements instead of computing the factorial formula by hand.
+Import `permutations` from the `itertools` module, read a line of space-separated names followed by a whole number R on the next line, and print how many permutations of length R exist for that list.
 ### Input Format
-- Line 1: Space-separated items
-- Line 2: R (the arrangement size)
+- Line 1: Space-separated names
+- Line 2: R, the length of each arrangement
 ### Output Format
 ```
 6
 ```
 ### Example Walkthrough
-For the sample input, the items are "a b c" (3 items) and R is 2. The number of ordered arrangements of 2 items chosen from 3 is `permutations(["a","b","c"], 2)`, which yields 6 arrangements (ab, ac, ba, bc, ca, cb), so the program prints 6.
+In the sample, the names are `a b c` and R is 2. There are 6 ways to arrange 2 names out of 3 in order (ab, ac, ba, bc, ca, cb), so the program prints `6`.
 ### Constraints
-- R is a non-negative integer not greater than the number of items.
+- R is a valid whole number no greater than the number of names given.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
@@ -7441,17 +7450,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A calendar app displays event dates to users with the full month name instead of a numeric month, to make the schedule easier to read. Import datetime from the datetime module, parse the input date using datetime.strptime with the format "%Y-%m-%d", and use strftime("%B") to print the full English month name of that date.
+          <t>A birthday reminder app converts a friend's birthdate, stored as `YYYY-MM-DD`, into a friendly month name to show in the notification, using Python's `datetime` module instead of a manual lookup table.
+Import `datetime` from the `datetime` module, read a date in `YYYY-MM-DD` format, and print the full name of its month.
 ### Input Format
-- Line 1: A date in YYYY-MM-DD format
+- Line 1: A date (YYYY-MM-DD)
 ### Output Format
 ```
 July
 ```
 ### Example Walkthrough
-For the sample input, the date is "2026-07-09". Parsing it with `datetime.strptime` gives month 07, and `strftime("%B")` converts month 07 to its full name, "July", so the program prints July.
+In the sample, the date is `2026-07-09`. The month number is 07, whose full name is `July`, so the program prints `July`.
 ### Constraints
-- The input is a valid calendar date in YYYY-MM-DD format.
+- The date is valid and formatted as `YYYY-MM-DD`.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>

--- a/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 10 - Modules and Packages/Unit 10 - Modules and Packages - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 10" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,17 +597,11 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Anil's family has bought a square plot for a kitchen garden, and the land record only mentions its total area. To order fencing, Anil needs the length of one side, which is the square root of the area. Import the math module and use math.sqrt to print the square root of the number read from input, rounded to 4 decimal places.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-4.0
-```
 ### Example Walkthrough
 For the sample input, the number is 16. `math.sqrt(16)` gives 4.0, and rounding to 4 decimal places leaves it as 4.0, so the program prints 4.0.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -742,9 +733,9 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>import math
+          <t>import math                              # math module provides precise math functions
 n = int(input())
-print(round(math.sqrt(n), 4))</t>
+print(round(math.sqrt(n), 4))            # math.sqrt computes an exact square root</t>
         </is>
       </c>
     </row>
@@ -757,17 +748,11 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Lakshmi notes down her marks from every weekly quiz and wants to know her average so far, without adding them up by hand. Python's statistics module can do this in one step. Use statistics.mean to print the average of a line of space-separated numbers, rounded to 2 decimal places.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2.5
-```
 ### Example Walkthrough
 For the sample input, the numbers are 1 2 3 4. Their total is 10 and there are 4 numbers, so the mean is 10 / 4 = 2.5, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -899,9 +884,9 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>import statistics
+          <t>import statistics                        # statistics module has ready-made average/median functions
 nums = list(map(int, input().split()))
-print(round(statistics.mean(nums), 2))</t>
+print(round(statistics.mean(nums), 2))   # mean() avoids writing sum(nums)/len(nums) by hand</t>
         </is>
       </c>
     </row>
@@ -914,18 +899,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>For Diwali, Deepa has 12 laddus and 18 barfis and wants to pack identical gift boxes with no sweets left over. The largest number of such boxes is the greatest common divisor of the two counts. Use 'from math import gcd' to print the greatest common divisor of the two numbers read from input.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-6
-```
 ### Example Walkthrough
 For the sample input, the numbers are 12 and 18. The largest number that divides both exactly is 6 (12 = 6 x 2 and 18 = 6 x 3), so `gcd(12, 18)` returns 6 and the program prints 6.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1064,7 +1042,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>from math import gcd
+          <t>from math import gcd                     # import just gcd, no need for a math. prefix
 a = int(input())
 b = int(input())
 print(gcd(a, b))</t>
@@ -1080,17 +1058,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>The gardening club is planning a circular flower bed in the middle of the college lawn and needs its area to order the right amount of soil. Instead of typing an approximate value of pi, use the accurate one from the math module. Use math.pi to print the area of a circle (pi * r * r) rounded to 2 decimal places, where r is the radius read from input.
-### Input Format
-- Line 1: Radius
-### Output Format
-```
-3.14
-```
 ### Example Walkthrough
 For the sample input, the radius is 1. The area is math.pi x 1 x 1, which is about 3.14159, and rounding to 2 decimal places gives 3.14, so the program prints 3.14.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1224,7 +1196,7 @@
         <is>
           <t>import math
 r = int(input())
-print(round(math.pi * r * r, 2))</t>
+print(round(math.pi * r * r, 2))         # math.pi is more accurate than typing 3.14</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1209,11 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>After the college fest, the organisers collect one-line feedback from visitors and want to know which word appears most often across a sentence. Python's collections module has a Counter that makes counting easy. Use collections.Counter to find the most common word in the sentence read from input, and print the word and its count separated by a space.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-a 3
-```
 ### Example Walkthrough
 For the sample input, the sentence is 'a b a c a'. Counting each word, 'a' appears 3 times while 'b' and 'c' appear once each, so the most common word is 'a' with count 3 and the program prints 'a 3'.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1379,9 +1345,9 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>from collections import Counter
+          <t>from collections import Counter          # Counter tallies items without a manual loop
 words = input().split()
-word, count = Counter(words).most_common(1)[0]
+word, count = Counter(words).most_common(1)[0]   # most_common(1) returns the top (item, count)
 print(word, count)</t>
         </is>
       </c>
@@ -1395,17 +1361,11 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Sanya's cousin has fixed a date for the family function, and Sanya wants to check which day of the week it falls on before booking her bus ticket home. Use the datetime module to print the day of the week (for example 'Monday') for a given date. Read a date written as YYYY-MM-DD from input.
-### Input Format
-- Line 1: A date as YYYY-MM-DD
-### Output Format
-```
-Monday
-```
 ### Example Walkthrough
 For the sample input, the date is 2024-01-01, which is 1 January 2024. The datetime module reports that this date falls on a Monday, so the program prints Monday.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1537,10 +1497,10 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>from datetime import date
+          <t>from datetime import date                # date handles calendar logic like weekdays
 parts = input().split("-")
 d = date(int(parts[0]), int(parts[1]), int(parts[2]))
-print(d.strftime("%A"))</t>
+print(d.strftime("%A"))                  # %A formats the date as its full weekday name</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1513,11 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>While signing up on a shopping website, users type a line of text, and the site wants to know how much of it is letters and how much is digits. Use the string module's `ascii_letters` and digits to count how many letters and how many digits are in a line of text read from input. Print the two counts separated by a space.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-3 3
-```
 ### Example Walkthrough
 For the sample input, the text is 'abc 123'. The characters a, b, c are letters (3 of them) and 1, 2, 3 are digits (3 of them), while the space is neither, so the program prints '3 3'.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1695,10 +1649,10 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>import string
+          <t>import string                            # string module holds ready-made character sets
 text = input()
-letters = sum(1 for c in text if c in string.ascii_letters)
-digits = sum(1 for c in text if c in string.digits)
+letters = sum(1 for c in text if c in string.ascii_letters)   # ascii_letters covers a-z and A-Z
+digits = sum(1 for c in text if c in string.digits)           # digits covers 0-9
 print(letters, digits)</t>
         </is>
       </c>
@@ -1712,18 +1666,11 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>The sports teacher has a squad of players and must pick a few of them for the doubles table-tennis team, and she is curious how many different teams are possible. Choosing r items from n items is exactly what math.comb computes. Use math.comb to print how many ways there are to choose r items from n items, where n and r are read from input.
-### Input Format
-- Line 1: n
-- Line 2: r
-### Output Format
-```
-10
-```
 ### Example Walkthrough
 For the sample input, n is 5 and r is 2. The number of ways to choose 2 players out of 5 is `math.comb(5, 2)` = 10, so the program prints 10.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1865,7 +1812,7 @@
           <t>import math
 n = int(input())
 r = int(input())
-print(math.comb(n, r))</t>
+print(math.comb(n, r))                   # math.comb counts selections where order doesn't matter</t>
         </is>
       </c>
     </row>
@@ -1879,17 +1826,11 @@
         <is>
           <t>A robotics workshop programs a servo arm using angles in radians internally, but the control panel needs to display the equivalent angle in degrees for the technician operating it.
 Import the `math` module and use `math.degrees` to convert an angle from radians to degrees, then print the result rounded to 2 decimal places.
-### Input Format
-- Line 1: An angle in radians
-### Output Format
-```
-180.0
-```
 ### Example Walkthrough
 In the sample, the angle is `3.141592653589793` radians (pi). `math.degrees(pi)` gives 180.0, so the program prints `180.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2022,7 +1963,7 @@
       <c r="AG10" t="inlineStr">
         <is>
           <t>import math
-print(round(math.degrees(float(input())),2))</t>
+print(round(math.degrees(float(input())),2))   # math.degrees converts radians to degrees</t>
         </is>
       </c>
     </row>
@@ -2036,17 +1977,11 @@
         <is>
           <t>A raffle app picks a winning color from four options, but for demo purposes the organizers want the pick to be reproducible: seeding the random number generator with a fixed number before choosing means the same seed always produces the same result.
 Import the `random` module, call `random.seed` with a whole number read from input, then use `random.choice` to pick one value from the list `["red", "blue", "green", "yellow"]` and print it.
-### Input Format
-- Line 1: A whole number used as the random seed
-### Output Format
-```
-blue
-```
 ### Example Walkthrough
 In the sample, the seed is 1. Seeding Python's random module with 1 and then calling `random.choice` on the color list deterministically picks `blue`, so the program prints `blue`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2178,469 +2113,269 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>import random
-random.seed(int(input()))
-print(random.choice(["red","blue","green","yellow"]))</t>
+          <t>import random                            # random module handles pseudo-random selection
+random.seed(int(input()))                # seeding makes the "random" pick reproducible
+print(random.choice(["red","blue","green","yellow"]))   # choice picks one item from the list</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Rotate with Deque</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>In Varun's hostel, the room-cleaning duty roster shifts every week: each name moves K places to the right, and names that fall off the end come back to the front. Use collections.deque and its rotate method to rotate a list of numbers to the right by K places. Read the numbers and K from input, and print the rotated list separated by spaces.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: K
-### Output Format
-```
-4 5 1 2 3
-```
 ### Example Walkthrough
 For the sample input, the list is 1 2 3 4 5 and K is 2. Rotating right by 2 moves the last two numbers, 4 and 5, to the front, giving 4 5 1 2 3, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 2</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>4 5 1 2 3</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>1 2 3
 0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>1 2
 3</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>2 1</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>5
 0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 5</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 -2</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>3 4 5 1 2</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 10</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>7 8 1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>from collections import deque
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>from collections import deque            # deque supports fast left/right rotation
 nums = deque(map(int, input().split()))
 k = int(input())
-nums.rotate(k)
+nums.rotate(k)                           # rotate(k) shifts elements right by k places
 print(*nums)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Sum of Fractions</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Amma's sweet recipe mixes several part-cup measures of milk, like half a cup and one-third of a cup, and she wants the exact total as a fraction, not a rounded decimal. Use fractions.Fraction to add N fractions and print the exact result in lowest terms as 'p/q'. Read N, then N fractions each written as 'a/b'.
-### Input Format
-- Line 1: N
-- Next N lines: a fraction 'a/b'
-### Output Format
-```
-5/6
-```
 ### Example Walkthrough
 For the sample input, N is 2 and the fractions are 1/2 and 1/3. Writing both with denominator 6 gives 3/6 + 2/6 = 5/6, which is already in lowest terms, so the program prints '5/6'.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>2
 1/2
 1/3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>5/6</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1
 2/4</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>3
 1/6
@@ -2648,33 +2383,33 @@
 1/6</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>1
 0/1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>4
 1/2
@@ -2683,2607 +2418,2337 @@
 1/2</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>2/1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>2
 1/3
 2/3</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>from fractions import Fraction
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>from fractions import Fraction           # Fraction keeps exact values instead of rounding
 n = int(input())
 total = Fraction(0)
 for _ in range(n):
-    total += Fraction(input())
-print(f"{total.numerator}/{total.denominator}")</t>
+    total += Fraction(input())           # Fraction("1/2") parses the a/b string directly
+print(f"{total.numerator}/{total.denominator}")   # always reduced to lowest terms</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Factorial from Math</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Use math.factorial to print the factorial of a number read from input.
-### Input Format
-- Line 1: A number
-### Output Format
-```
-120
-```
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A college fest's event-scheduling app tells organizers exactly how many distinct running orders are possible for the performers booked on a stage, so they know how much flexibility they have while finalizing the lineup. The number of running orders for n performers is n factorial.
+Read a whole number and use `math.factorial` to print the factorial of that number.
 ### Example Walkthrough
 In the sample, the number is `5`. Its factorial is `5 x 4 x 3 x 2 x 1 = 120`, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>3628800</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>5040</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>479001600</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>import math
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>import math                              # math module already implements factorial
 print(math.factorial(int(input())))</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Floor and Ceiling</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read a decimal number and use math.floor and math.ceil to print its floor and ceiling, separated by a space.
-### Input Format
-- Line 1: A decimal number
-### Output Format
-```
-3 4
-```
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A food-delivery app's billing utility needs to show riders both the rounded-down and rounded-up versions of a fare so support staff can quickly check whether a customer was charged fairly. Given the raw fare amount, the tool must report its floor and its ceiling.
+Read a decimal number and use `math.floor` and `math.ceil` to print its floor and ceiling, separated by a space.
 ### Example Walkthrough
-In the sample, the number is `3.2`. Its floor is `3` and its ceiling is `4`, so the program prints `3 4`.
+In the sample, the number is `3.4`. Its floor is `3` and its ceiling is `4`, so the program prints `3 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>3 4</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>5 5</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>-2.5</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>-3 -2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>-1 0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>99.99</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>99 100</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>-100.01</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>-101 -100</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>import math
 x = float(input())
-print(math.floor(x), math.ceil(x))</t>
+print(math.floor(x), math.ceil(x))       # floor rounds down, ceil rounds up</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Median with Statistics</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Use statistics.median to print the median of a line of numbers.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2
-```
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A class teacher's marks dashboard highlights the median score for every test so parents get a sense of the 'typical' performance without it being skewed by a few very high or very low marks. Given one line of marks, the dashboard needs the middle value.
+Read a line of numbers and use `statistics.median` to print their median.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3`. The middle value is `2`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1 2 3</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>1 2 3 4</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>-3 -1 -2</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>15.0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>import statistics
 nums = list(map(int, input().split()))
-print(statistics.median(nums))</t>
+print(statistics.median(nums))           # median sorts internally and picks the middle value</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Power from Math</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Use math.pow to print a raised to the power b as a whole number.
-### Input Format
-- Line 1: base
-- Line 2: exponent
-### Output Format
-```
-1024
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A bank's compound-interest calculator lets customers see how much a fixed principal would multiply by if a base growth factor were applied repeatedly for a number of years. Given a base and an exponent, the calculator needs the base raised to that power as a whole number.
+Read a base `a` and an exponent `b`, then use `math.pow` to print `a` raised to the power `b`, rounded to a whole number.
 ### Example Walkthrough
 In the sample, the base is `2` and the exponent is `10`. Computing `2` raised to the power `10` gives `1024`, so the program prints `1024`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>3
 0</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>5
 2</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>1
 100</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>10
 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>-2
 3</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>import math
 base = int(input())
 exp = int(input())
-print(round(math.pow(base, exp)))</t>
+print(round(math.pow(base, exp)))        # math.pow always returns a float, so round it</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Hypotenuse</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Use math.hypot to print the length of the hypotenuse of a right triangle given its two shorter sides, rounded to 2 decimal places.
-### Input Format
-- Line 1: First side
-- Line 2: Second side
-### Output Format
-```
-5.0
-```
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A carpentry workshop app helps apprentices cut a diagonal support brace to the right length. Given the lengths of the two perpendicular sides of a right-angled frame, the app needs the length of the diagonal brace connecting their ends.
+Read the two shorter sides of a right triangle and use `math.hypot` to print the length of the hypotenuse, rounded to 2 decimal places.
 ### Example Walkthrough
 In the sample, the two sides are `3` and `4`. The hypotenuse is `sqrt(3^2 + 4^2) = 5.0`, so the program prints `5.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>5
 12</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>8
 15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>17.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>141.42</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>import math
 a = int(input())
 b = int(input())
-print(round(math.hypot(a, b), 2))</t>
+print(round(math.hypot(a, b), 2))        # hypot computes sqrt(a**2 + b**2) directly</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Base-10 Logarithm</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Use math.log10 to print the base-10 logarithm of a number, rounded to 4 decimal places.
-### Input Format
-- Line 1: A positive number
-### Output Format
-```
-2.0
-```
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A sound-engineering app converts raw signal-power ratios into a more intuitive logarithmic scale before displaying them on a mixing console. Given a power ratio, the tool needs its base-10 logarithm.
+Read a number and use `math.log10` to print its base-10 logarithm, rounded to 4 decimal places.
 ### Example Walkthrough
 In the sample, the number is `100`. Its base-10 logarithm is `2.0`, so the program prints `2.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>0.699</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>2.9996</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
-print(round(math.log10(n), 4))</t>
+print(round(math.log10(n), 4))           # log10 is more accurate than log(n, 10)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Days Difference</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A hotel booking app calculates the number of nights between a guest's check-in date and check-out date, regardless of which one was typed first.
 Import `datetime` from the `datetime` module, read two dates in `YYYY-MM-DD` format, and print the absolute number of days between them.
-### Input Format
-- Line 1: First date (YYYY-MM-DD)
-- Line 2: Second date (YYYY-MM-DD)
-### Output Format
-```
-1
-```
 ### Example Walkthrough
 In the sample, the dates are `2026-01-01` and `2026-01-02`. The difference between them is 1 day, so the program prints `1`.
 ### Constraints
 - Dates are valid and formatted as `YYYY-MM-DD`.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>datetime-module</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>2026-01-01
 2026-01-02</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>2026-01-10
 2026-01-01</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>2024-02-28
 2024-03-01</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>2026-07-09
 2026-07-09</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>2025-12-31
 2026-01-01</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>2020-01-01
 2020-01-31</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>2026-05-01
 2026-04-01</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>from datetime import datetime
-a=datetime.strptime(input(),"%Y-%m-%d"); b=datetime.strptime(input(),"%Y-%m-%d")
-print(abs((b-a).days))</t>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>from datetime import datetime            # datetime supports subtracting dates directly
+a=datetime.strptime(input(),"%Y-%m-%d"); b=datetime.strptime(input(),"%Y-%m-%d")   # strptime parses text into a date object
+print(abs((b-a).days))                   # subtracting dates gives a timedelta with .days</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Import Alias Sqrt</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A packing app calculates the largest complete square grid of boxes that fit inside a warehouse holding N boxes total, using an integer square root so the result is always a whole number of boxes per side.
 Import the `math` module under the shorter alias `m` (`import math as m`), then use `m.isqrt` to compute the integer square root of a whole number read from input, and print the result.
-### Input Format
-- Line 1: A whole number
-### Output Format
-```
-4
-```
 ### Example Walkthrough
 In the sample, the number is 16. `m.isqrt(16)` returns 4 (since 4 x 4 = 16 exactly), so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid non-negative whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>12345</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>import math as m
-print(m.isqrt(int(input())))</t>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>import math as m                         # alias shortens math. to m. at every call site
+print(m.isqrt(int(input())))             # isqrt gives an exact integer square root</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Standard Deviation</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Use statistics.pstdev to print the population standard deviation of a line of numbers, rounded to 2 decimal places.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-1.41
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The class-marks dashboard also reports how spread out a test's scores are, so a teacher can tell a tightly clustered class apart from one with wildly varying performance. Given one line of marks, the dashboard needs the population standard deviation.
+Read a line of numbers and use `statistics.pstdev` to print their population standard deviation, rounded to 2 decimal places.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4 5`. Their population standard deviation, rounded to 2 decimal places, is `1.41`, so the program prints `1.41`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>10 10 10</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>2 4 6</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>-5 5 -5 5</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>2.87</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>100 200</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>import statistics
 nums = list(map(int, input().split()))
-print(round(statistics.pstdev(nums), 2))</t>
+print(round(statistics.pstdev(nums), 2))   # pstdev computes population standard deviation</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - GCD of a List</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Use functools.reduce together with math.gcd to print the greatest common divisor of a whole line of numbers.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-6
-```
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A recipe app lets a home cook scale a dish up or down and wants to simplify the resulting ingredient-ratio numbers to their smallest whole-number form. Before it can do that, it needs the greatest common divisor shared by every quantity in the recipe.
+Read a line of numbers and use `functools.reduce` together with `math.gcd` to print the greatest common divisor of the whole list.
 ### Example Walkthrough
 In the sample, the numbers are `12 18 24`. Their greatest common divisor is `6`, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>12 18 24</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>7 14</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>100 25 50</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>0 5</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>1000 500 250 100</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>from functools import reduce
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>from functools import reduce             # reduce applies a function cumulatively across a list
 from math import gcd
 nums = list(map(int, input().split()))
-print(reduce(gcd, nums))</t>
+print(reduce(gcd, nums))                 # reduces the whole list to a single overall gcd</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Count Permutations</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Use math.perm to print how many ordered arrangements there are of r items chosen from n items.
-### Input Format
-- Line 1: n
-- Line 2: r
-### Output Format
-```
-20
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The same event-scheduling app also needs to tell organizers how many ways a smaller number of opening-segment slots can be filled by choosing and ordering acts from the full lineup, since only a few acts fit before the interval. Given the total number of acts n and the number of slots r, it needs the count of ordered arrangements.
+Read `n` and `r`, then use `math.perm` to print how many ordered arrangements there are of `r` items chosen from `n` items.
 ### Example Walkthrough
 In the sample, `n` is `5` and `r` is `2`. The number of ordered arrangements of `2` items from `5` is `5 x 4 = 20`, so the program prints `20`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>5
 2</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>4
 4</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>6
 1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>10
 0</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
 r = int(input())
-print(math.perm(n, r))</t>
+print(math.perm(n, r))                   # math.perm counts arrangements where order matters</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Group by Parity</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Use collections.defaultdict to split a line of numbers into evens and odds. Print 'even:' followed by the even numbers, then 'odd:' followed by the odd numbers, keeping their original order.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-even: 2 4
-odd: 1 3 5
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A music app's playlist shuffler gives listeners a quick way to split a queue of track numbers into two mini-playlists — one built from evenly numbered tracks and one from oddly numbered tracks — while keeping each group in its original queue order.
+Read a line of numbers and use `collections.defaultdict` to split them into evens and odds. Print `'even:'` followed by the even numbers, then `'odd:'` followed by the odd numbers, keeping their original order.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 3 4 5`. The even ones are `2` and `4`, and the odd ones are `1`, `3`, and `5`, so the program prints `even: 2 4` then `odd: 1 3 5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1 2 3 4 5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>even: 2 4
 odd: 1 3 5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>2 4</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>even: 2 4
 odd:</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>1 3</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>even:
 odd: 1 3</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>even: 0
 odd:</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>-2 -1 0 1 2</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>even: -2 0 2
 odd: -1 1</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>even: 2 4 6 8 10
 odd: 1 3 5 7 9</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>even:
 odd: 7</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>from collections import defaultdict
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>from collections import defaultdict      # defaultdict avoids checking if a key already exists
 groups = defaultdict(list)
 for x in map(int, input().split()):
-    groups["even" if x % 2 == 0 else "odd"].append(x)
+    groups["even" if x % 2 == 0 else "odd"].append(x)   # missing keys default to an empty list
 print("even:", *groups["even"])
 print("odd:", *groups["odd"])</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Seeded Random</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Use the random module. Read a seed, seed the generator with it, and print a single random integer from 1 to 100. Seeding makes the result repeatable.
-### Input Format
-- Line 1: The seed
-### Output Format
-```
-18
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A quiz app's testing team wants to pick a random question for a demo but needs the exact same 'random' question to show up every time they rerun the demo, so they can rehearse the walkthrough. Fixing the random generator's seed before drawing a number makes the result repeatable.
+Read a seed, use the `random` module to seed the generator with it, and print a single random integer from 1 to 100.
 ### Example Walkthrough
 In the sample, the seed is `1`. Seeding the generator with `1` and then requesting a random integer from `1` to `100` deterministically produces `18`, so the program prints `18`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>random-module</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>12345</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>import random
 seed = int(input())
-random.seed(seed)
-print(random.randint(1, 100))</t>
+random.seed(seed)                        # seeding fixes the sequence so it's repeatable
+print(random.randint(1, 100))            # randint includes both endpoints</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Find the Mode</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Use statistics.mode to print the value that appears most often in a line of numbers.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-2
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The class-marks dashboard also flags the single score that came up most often in a test, since a teacher often wants to know the most common mark before deciding how to curve the results.
+Read a line of numbers and use `statistics.mode` to print the value that appears most often.
 ### Example Walkthrough
 In the sample, the numbers are `1 2 2 3`. The value `2` appears most often, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>1 2 2 3</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>1 1 2 2</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>-1 -1 -2</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>1 2 3 3 3 4</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>9 9 9 9 9 9</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>import statistics
 nums = list(map(int, input().split()))
-print(statistics.mode(nums))</t>
+print(statistics.mode(nums))             # mode returns the most frequently occurring value</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Top K Words</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Use collections.Counter to print the K most common words in a sentence, one 'word count' per line, from most to least common.
-### Input Format
-- Line 1: K
-- Line 2: A sentence
-### Output Format
-```
-a 3
-b 2
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A campus search engine's ranking tool wants to show which query words appear most often across a stretch of indexed text, so the most relevant keywords can be highlighted first.
+Read a value `K` and a line of words, then use `collections.Counter` to print the `K` most common words, one `'word count'` per line, from most to least common.
 ### Example Walkthrough
-In the sample, `K` is `2` and the sentence is `a b a c a b`. The word `a` appears `3` times and `b` appears `2` times, more than `c`, so the program prints `a 3` then `b 2`.
+In the sample, `K` is `2` and the sentence is `a b a c b a`. The word `a` appears `3` times and `b` appears `2` times, more than `c`, so the program prints `a 3` then `b 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>2
 a b a c b a</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>a 3
 b 2</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>1
 x x y</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>x 2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>3
 p q r</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>p 1
 q 1
 r 1</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>1
 z</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>z 1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>0
 a b c</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>5
 a a b b c c d</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>a 2
 b 2
@@ -5291,1005 +4756,789 @@
 d 1</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>2
 cat cat dog dog dog bird</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>dog 3
 cat 2</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>from collections import Counter
 k = int(input())
 words = input().split()
-for word, count in Counter(words).most_common(k):
+for word, count in Counter(words).most_common(k):   # most_common(k) returns the top k, already sorted
     print(word, count)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Path Suffix</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A file upload service checks the extension of every uploaded file's name to decide which validator to run, using the `Path` class from the `pathlib` module instead of manually searching for the last dot.
 Import `Path` from the `pathlib` module, read a file name or path, and print its file extension (including the leading dot) using the `.suffix` property. If the file has no extension, print an empty line.
-### Input Format
-- Line 1: A file name or path
-### Output Format
-```
-.csv
-```
 ### Example Walkthrough
 In the sample, the input is `report.csv`. `Path("report.csv").suffix` returns `.csv`, so the program prints `.csv`.
 ### Constraints
 - The input is a valid file name or path.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>pathlib-module</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>report.csv</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>.csv</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>/tmp/data.json</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>.json</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>archive.tar.gz</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>.gz</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>README</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>notes.txt</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>.txt</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>a/b/c.py</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>.py</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>image.PNG</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>.PNG</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>from pathlib import Path
-print(Path(input()).suffix)</t>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>from pathlib import Path                 # Path offers file-path helpers like .suffix
+print(Path(input()).suffix)              # suffix extracts the extension, including the dot</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Counter Import</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A word-frequency analyzer needs to know which single character appears most often in a block of text, using the `Counter` class from the `collections` module to tally every character instantly instead of writing a manual loop.
 Import `Counter` from the `collections` module, read a line of text, and use `Counter` together with `most_common(1)` to find the character that appears most often and how many times it appears, then print the character and the count separated by a space.
-### Input Format
-- Line 1: A line of text
-### Output Format
-```
-a 3
-```
 ### Example Walkthrough
 In the sample, the text is `banana`. Counting each character, `a` appears 3 times, more than any other character, so the program prints `a 3`.
 ### Constraints
 - The input is a valid, non-empty line of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>banana</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>a 3</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>l 2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>a 1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>mississippi</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>i 4</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>bookkeeper</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>e 3</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>112233</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>zzzy</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>z 3</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>from collections import Counter
-ch,c=Counter(input()).most_common(1)[0]
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>from collections import Counter          # Counter works on any iterable, including strings
+ch,c=Counter(input()).most_common(1)[0]  # counts each character and picks the top one
 print(ch,c)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - OS Basename</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A file manager app needs to display just the file (or folder) name at the end of a full file path, without the rest of the directory structure, using the `os.path` module instead of splitting the string manually.
 Import the `os` module, read a file path, and print just the final component of the path (the file or folder name) using `os.path.basename`, after removing any trailing slash.
-### Input Format
-- Line 1: A file path
-### Output Format
-```
-a.txt
-```
 ### Example Walkthrough
 In the sample, the path is `/home/user/a.txt`. `os.path.basename` returns just the final component, `a.txt`, which the program prints.
 ### Constraints
 - The input is a valid file path.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>os-module</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>/home/user/a.txt</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>a.txt</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>report.csv</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>report.csv</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>folder/sub/file.py</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>file.py</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>/tmp/</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>tmp</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>C:/data/test.txt</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>test.txt</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>README</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>README</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>a/b/c</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>import os
-print(os.path.basename(input().rstrip("/")))</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>import os                                # os.path gives platform-safe path handling
+print(os.path.basename(input().rstrip("/")))   # basename returns the last part of a path</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Pairs from Combinations</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Use itertools.combinations to count how many pairs of numbers add up to a target. Read a line of numbers and a target and print the count.
-### Input Format
-- Line 1: Space-separated numbers
-- Line 2: Target
-### Output Format
-```
-2
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A tournament organizer's pairing app wants to know how many possible player pairs would combine for a total score exactly equal to a target value, before it finalizes the matchups. Given a line of scores and a target, it needs to count how many unique pairs of scores add up to that target.
+Read a line of numbers and a target, then use `itertools.combinations` to print how many pairs of numbers add up to the target.
 ### Example Walkthrough
-In the sample, the numbers are `1 2 3 4 5` and the target is `6`. The pairs `(1, 5)` and `(2, 4)` both add up to `6`, so the program prints `2`.
+In the sample, the numbers are `1 2 3 4` and the target is `5`. The pairs `(1, 4)` and `(2, 3)` both add up to `5`, so the program prints `2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>1 2 3 4
 5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>1 1 1
 2</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>5 6
 100</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>0 0 0
 0</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8
 9</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>-1 1 -2 2
 0</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>from itertools import combinations
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>from itertools import combinations       # combinations generates all unique pairs
 nums = list(map(int, input().split()))
 target = int(input())
-print(sum(1 for a, b in combinations(nums, 2) if a + b == target))</t>
+print(sum(1 for a, b in combinations(nums, 2) if a + b == target))   # counts pairs matching the target</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Days Between Dates</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Use the datetime module to print how many days apart two dates are (a non-negative number). Read two dates written as YYYY-MM-DD.
-### Input Format
-- Line 1: First date
-- Line 2: Second date
-### Output Format
-```
-30
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>An HR leave-management app needs to tell an employee exactly how many calendar days separate the start and end dates of a requested leave period, so it can validate that against the days remaining in their annual quota.
+Read two dates written as `YYYY-MM-DD` and use the `datetime` module to print how many days apart they are (a non-negative number).
 ### Example Walkthrough
 In the sample, the dates are `2024-01-01` and `2024-01-31`. They are `30` days apart, so the program prints `30`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>datetime-module</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>2024-01-01
 2024-01-31</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>2024-01-01
 2024-01-01</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>2020-01-01
 2021-01-01</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>366</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>2024-03-01
 2024-01-01</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>1970-01-01
 1970-01-01</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>2000-02-29
 2000-03-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>1999-12-31
 2000-01-01</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>from datetime import date
 def parse(s):
@@ -6297,1305 +5546,1256 @@
     return date(int(y), int(m), int(d))
 d1 = parse(input())
 d2 = parse(input())
-print(abs((d2 - d1).days))</t>
+print(abs((d2 - d1).days))               # date subtraction gives a timedelta with .days</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Common Words with Counts</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Use Counter intersection (the &amp; operator) to find words appearing in both of two lines. For each shared word in sorted order, print 'word:count' where count is the smaller of the two counts.
-### Input Format
-- Line 1: First sentence
-- Line 2: Second sentence
-### Output Format
-```
-a:1
-b:1
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The same campus search-ranking tool also compares two indexed pages to find keywords that show up on both, since a word shared by two pages is a stronger relevance signal than one appearing on only one page.
+Read two lines of words, then use Counter intersection (the `&amp;` operator) to find words appearing in both lines. For each shared word in sorted order, print `'word:count'` where count is the smaller of the two counts.
 ### Example Walkthrough
-In the sample, the sentences are `a b c` and `a b d`. The words `a` and `b` appear in both, once each, so the program prints `a:1` then `b:1`.
+In the sample, the sentences are `a a b c` and `a b b`. The word `a` appears twice in the first line and once in the second, so its shared count is `1`; the word `b` appears once in the first line and twice in the second, so its shared count is also `1`. The program prints `a:1` then `b:1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>a a b c
 a b b</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>a:1
 b:1</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>x y
 y z</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>y:1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>p p
 p p p</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>p:2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>x
 x</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>x:1</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>a b c d
 e f g h</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>cat cat dog
 dog dog cat</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>cat:1
 dog:1</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>from collections import Counter
 c1 = Counter(input().split())
 c2 = Counter(input().split())
-shared = c1 &amp; c2
+shared = c1 &amp; c2                         # &amp; keeps the smaller count for words in both
 for word in sorted(shared):
     print(f"{word}:{shared[word]}")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Leap Year Check</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Use calendar.isleap to print 'Yes' if a year is a leap year and 'No' otherwise.
-### Input Format
-- Line 1: A year
-### Output Format
-```
-Yes
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A calendar app needs to decide whether February should show 28 or 29 days for a given year before it draws the month grid.
+Read a year and use `calendar.isleap` to print `'Yes'` if it is a leap year and `'No'` otherwise.
 ### Example Walkthrough
-In the sample, the year is `2024`, which is divisible by `4` and not a century year, so it is a leap year and the program prints `Yes`.
+In the sample, the year is `2000`. It is divisible by `4`, and even though it is a century year it is also divisible by `400`, so it is a leap year and the program prints `Yes`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>import calendar
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>import calendar                          # calendar module knows leap-year rules
 year = int(input())
-print("Yes" if calendar.isleap(year) else "No")</t>
+print("Yes" if calendar.isleap(year) else "No")   # isleap handles century-year exceptions too</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Exact Decimal Sum</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Use decimal.Decimal to add two decimal numbers without floating-point rounding error, and print the exact sum. Read the two numbers as text.
-### Input Format
-- Line 1: First decimal
-- Line 2: Second decimal
-### Output Format
-```
-0.3
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>An e-commerce billing app must add up two currency amounts without introducing floating-point rounding errors that could make an invoice off by a fraction of a rupee.
+Read two decimal numbers as text and use `decimal.Decimal` to add them without floating-point rounding error, then print the exact sum.
 ### Example Walkthrough
 In the sample, the numbers are `0.1` and `0.2`. Using `Decimal` avoids floating-point rounding error, so the exact sum `0.3` is printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>0.1
 0.2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>1.5
 2.5</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>0.01
 0.02</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>-1.5
 1.5</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>100.001
 0.999</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>101.000</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>-0.1
 -0.2</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>from decimal import Decimal
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>from decimal import Decimal              # Decimal avoids binary floating-point rounding
 a = Decimal(input())
 b = Decimal(input())
 print(a + b)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - K Largest with Heapq</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Use heapq.nlargest to print the K largest numbers from a list, in descending order, separated by spaces.
-### Input Format
-- Line 1: K
-- Line 2: Space-separated numbers
-### Output Format
-```
-5 4
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A gaming leaderboard needs to spotlight the top few scores from a long list of session results without sorting the entire list.
+Read a value `K` and a line of numbers, then use `heapq.nlargest` to print the `K` largest numbers, in descending order, separated by spaces.
 ### Example Walkthrough
 In the sample, `K` is `2` and the numbers are `3 1 4 1 5`. The two largest values are `5` and `4`, so the program prints `5 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>2
 3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>5 4</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>1
 7 2</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>3
 5 5 5</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>0
 1 2 3</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>5
 1 2 3 4 5 6 7 8 9 10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>10 9 8 7 6</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>2
 -5 -1 -10</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>-1 -5</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>import heapq
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>import heapq                             # heapq is efficient for finding top/bottom values
 k = int(input())
 nums = list(map(int, input().split()))
-print(*heapq.nlargest(k, nums))</t>
+print(*heapq.nlargest(k, nums))          # nlargest returns the k biggest, already sorted</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Prime Factors</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Use math.isqrt to help print the prime factors of a number in increasing order, separated by spaces (a factor is listed once for each time it divides the number).
-### Input Format
-- Line 1: A whole number greater than 1
-### Output Format
-```
-2 2 3
-```
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A cryptography teaching tool shows students why factoring large numbers is hard by breaking a smaller demo number down into its prime building blocks.
+Read a number and use `math.isqrt` to help print its prime factors in increasing order, separated by spaces (a factor is listed once for each time it divides the number).
 ### Example Walkthrough
 In the sample, the number is `12`. Its prime factors are `2`, `2`, and `3` (since `2 x 2 x 3 = 12`), so the program prints `2 2 3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>math-module</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>2 2 3</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>2 2 3 5</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>2 2 2 2 2 2 2 2 2 2</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>3 3 3 37</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>import math
 n = int(input())
 factors = []
 d = 2
-while d &lt;= math.isqrt(n):
+while d &lt;= math.isqrt(n):                # isqrt avoids float errors from math.sqrt
     while n % d == 0:
         factors.append(d)
         n //= d
     d += 1
 if n &gt; 1:
-    factors.append(n)
+    factors.append(n)                    # a leftover n greater than 1 is itself prime
 print(*factors)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Decimal Addition</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A billing system adds two currency amounts together and must avoid the tiny rounding errors that plain floating-point addition can introduce (like `0.1 + 0.2` not printing exactly `0.3`), so it uses the `Decimal` class from the `decimal` module instead.
 Import `Decimal` from the `decimal` module, read two numbers as text, convert each to a `Decimal`, and print their sum.
-### Input Format
-- Line 1: First amount
-- Line 2: Second amount
-### Output Format
-```
-0.3
-```
 ### Example Walkthrough
 In the sample, the amounts are `0.1` and `0.2`. Adding them as `Decimal` values gives exactly `0.3`, with none of the rounding drift that ordinary floating-point addition can produce, so the program prints `0.3`.
 ### Constraints
 - The inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>0.1
 0.2</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>1.5
 2.25</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>100
 0.01</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>100.01</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>-1.1
 1.1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>999.99
 0.01</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>1000.00</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>123.456
 0.004</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>123.460</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>from decimal import Decimal
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>from decimal import Decimal              # Decimal keeps exact precision for currency math
 print(Decimal(input())+Decimal(input()))</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Permutations Count</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>An event scheduler needs to know how many different ways it can arrange a subset of R speakers, in order, from a longer list of available speakers, using `itertools.permutations` to count the arrangements instead of computing the factorial formula by hand.
 Import `permutations` from the `itertools` module, read a line of space-separated names followed by a whole number R on the next line, and print how many permutations of length R exist for that list.
-### Input Format
-- Line 1: Space-separated names
-- Line 2: R, the length of each arrangement
-### Output Format
-```
-6
-```
 ### Example Walkthrough
 In the sample, the names are `a b c` and R is 2. There are 6 ways to arrange 2 names out of 3 in order (ab, ac, ba, bc, ca, cb), so the program prints `6`.
 ### Constraints
 - R is a valid whole number no greater than the number of names given.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>modules-and-packages</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>importing-modules</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>a b c
 2</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>x y
 2</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>1 2 3 4
 1</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>a
 1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>p q r
 3</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>a b c d
 2</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>z
 0</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>from itertools import permutations
-print(sum(1 for _ in permutations(input().split(), int(input()))))</t>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>from itertools import permutations       # permutations counts ordered arrangements
+print(sum(1 for _ in permutations(input().split(), int(input()))))   # generate and count all of length R</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Date Month Name</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A birthday reminder app converts a friend's birthdate, stored as `YYYY-MM-DD`, into a friendly month name to show in the notification, using Python's `datetime` module instead of a manual lookup table.
 Import `datetime` from the `datetime` module, read a date in `YYYY-MM-DD` format, and print the full name of its month.
-### Input Format
-- Line 1: A date (YYYY-MM-DD)
-### Output Format
-```
-July
-```
 ### Example Walkthrough
 In the sample, the date is `2026-07-09`. The month number is 07, whose full name is `July`, so the program prints `July`.
 ### Constraints
 - The date is valid and formatted as `YYYY-MM-DD`.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>standard-library</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>datetime-module</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>2024-02-29</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2020-05-15</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>1999-09-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>2030-03-01</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>from datetime import datetime
-print(datetime.strptime(input(),"%Y-%m-%d").strftime("%B"))</t>
+print(datetime.strptime(input(),"%Y-%m-%d").strftime("%B"))   # %B formats the date as its full month name</t>
         </is>
       </c>
     </row>
